--- a/output/2026-09-12_20_Croazia_Karlovacka_Utensilerie_e_Macchine_Utensili.xlsx
+++ b/output/2026-09-12_20_Croazia_Karlovacka_Utensilerie_e_Macchine_Utensili.xlsx
@@ -727,7 +727,7 @@
       <c r="F8" s="2" t="inlineStr"/>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>Verificata via WebSearch (fininfo.hr, tvrtke.hr, facebook): Selce 9/A, Karlovac, obrt per produzione/servizio/vendita di utensili e macchine per la lavorazione di legno, metallo ecc., tradizione dal 1979. Non e un cliente finale: vende e assiste utensili per terzi, non esercita in proprio attivita di officina/carpenteria.</t>
+          <t>Verificata via WebSearch (fininfo.hr, tvrtke.hr, facebook): Selce 9/A, Karlovac, obrt per produzione/servizio/vendita di utensili e macchine per la lavorazione di legno, metallo ecc., tradizione dal 1979. Non e un cliente finale: vende e assiste utensili per terzi, non esercita in proprio attivita di officina/carpenteria. [DUPLICATO — vedi anche: 2026-09-08_06_Croazia_Krapinsko-zagorska_Utensilerie_e_Macchine_Utensili.xlsx]</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">

--- a/output/2026-09-12_20_Croazia_Karlovacka_Utensilerie_e_Macchine_Utensili.xlsx
+++ b/output/2026-09-12_20_Croazia_Karlovacka_Utensilerie_e_Macchine_Utensili.xlsx
@@ -516,7 +516,7 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (14/09/2026)</t>
         </is>
       </c>
     </row>
@@ -554,7 +554,7 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (14/09/2026)</t>
         </is>
       </c>
     </row>
@@ -592,7 +592,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (14/09/2026)</t>
         </is>
       </c>
     </row>
@@ -626,7 +626,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (14/09/2026)</t>
         </is>
       </c>
     </row>
@@ -656,7 +656,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (14/09/2026)</t>
         </is>
       </c>
     </row>
@@ -698,7 +698,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (14/09/2026)</t>
         </is>
       </c>
     </row>
@@ -774,7 +774,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (14/09/2026)</t>
         </is>
       </c>
     </row>
@@ -812,7 +812,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (14/09/2026)</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (14/09/2026)</t>
         </is>
       </c>
     </row>
@@ -888,7 +888,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (14/09/2026)</t>
         </is>
       </c>
     </row>
@@ -930,7 +930,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (14/09/2026)</t>
         </is>
       </c>
     </row>
